--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$H$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$L$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$K$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Fit-Gap'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -790,7 +790,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>BIBS reference FR</t>
+          <t>Feature list reference</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>FR of the BIBS FRS BRD-2</t>
+          <t>Rows of the BIBS Feature List vs OOTB workbook</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Feature list reference</t>
+          <t>What BIBS offers out of the box</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Rows of the BIBS Feature List vs OOTB workbook</t>
+          <t>Standard capability or configuration</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>Insurance-broking best practice</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Standard capability or configuration</t>
+          <t>Practice of the Philippine market and international broking</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
@@ -1321,15 +1321,19 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Insurance-broking best practice</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Practice of the Philippine market and international broking</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr"/>
+          <t>Fit class</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Fit, Configure, Extend, Recommend change, Removed from the BRD, Specified in another FRS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -1339,19 +1343,15 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Recommendation</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Fit class</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Fit, Configure, Extend, Recommend change, Removed from the BRD, Specified in another FRS</t>
-        </is>
-      </c>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>What to do</t>
+          <t>Where it lands</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr"/>
@@ -1379,36 +1379,18 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>In the BIBS environment</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Where it lands</t>
+          <t>Available / Partly available / Planned for</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Fit-Gap</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>In the BIBS environment</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Available / Partly available / Planned for</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D24"/>
+  <autoFilter ref="A4:D23"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2210,21 +2192,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2253,7 +2234,6 @@
       <c r="I3" s="24" t="n"/>
       <c r="J3" s="24" t="n"/>
       <c r="K3" s="24" t="n"/>
-      <c r="L3" s="24" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
@@ -2278,40 +2258,35 @@
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t>BIBS reference FR</t>
+          <t>Feature list reference</t>
         </is>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>Feature list reference</t>
+          <t>What BIBS offers out of the box</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>Insurance-broking best practice</t>
         </is>
       </c>
       <c r="H4" s="25" t="inlineStr">
         <is>
-          <t>Insurance-broking best practice</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Recommendation</t>
         </is>
       </c>
       <c r="J4" s="25" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="K4" s="25" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>In the BIBS environment</t>
         </is>
@@ -2340,40 +2315,35 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sign-in, roles and permissions per action and segregation of duties are standard; the Cashiering permissions are given to the roles by configuration (Appendix H).</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Sign-in, roles and permissions per action and segregation of duties are standard; the Cashiering permissions are given to the roles by configuration (Appendix H).</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
           <t>Least privilege and four eyes on every cash movement; access only from managed devices (BSP IT risk management guidelines; ISO 27001 access control).</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the access matrix in the User Access Maintenance FRS; enforce BDO-issued devices through the network policy.</t>
+        </is>
+      </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>Confirm the access matrix in the User Access Maintenance FRS; enforce BDO-issued devices through the network policy.</t>
+          <t>FRS.CSH.01.01, 01.02; Appendix H</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.01.01, 01.02; Appendix H</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2402,40 +2372,35 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-002</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sign-in, roles and permissions per action and segregation of duties are standard; the Cashiering permissions are given to the roles by configuration (Appendix H).</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Sign-in, roles and permissions per action and segregation of duties are standard; the Cashiering permissions are given to the roles by configuration (Appendix H).</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
           <t>Least privilege and four eyes on every cash movement; access only from managed devices (BSP IT risk management guidelines; ISO 27001 access control).</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the access matrix in the User Access Maintenance FRS; enforce BDO-issued devices through the network policy.</t>
+        </is>
+      </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Confirm the access matrix in the User Access Maintenance FRS; enforce BDO-issued devices through the network policy.</t>
+          <t>FRS.CSH.01.01, 01.02; Appendix H</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.01.01, 01.02; Appendix H</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2464,40 +2429,35 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-003</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Role home pages with live work counts are standard; the Cashiering dashboard with count and amount per receipt type and status is an extension (the counts are available, the amounts per type follow BDOI's FRS.CSH.01.03.02).</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Role home pages with live work counts are standard; the Cashiering dashboard with count and amount per receipt type and status is an extension (the counts are available, the amounts per type follow BDOI's FRS.CSH.01.03.02).</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
           <t>A cashier's work queue by status with amounts, so that the day closes with nothing For Posting.</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>Add the amounts and the per-type items of BDOI's dashboard.</t>
+        </is>
+      </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Add the amounts and the per-type items of BDOI's dashboard.</t>
+          <t>FRS.CSH.01.03</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.01.03</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2526,40 +2486,35 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-130</t>
+          <t>INT-006 PMS post-dated cheque list (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>INT-006 PMS post-dated cheque list (OOTB: Partial)</t>
+          <t>File uploads with runs, records and alerts, and the exchanges between the BIBS modules are standard; the MFT intake of the OBPCS and PMS files is an extension to agree with BDOI IT.</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>File uploads with runs, records and alerts, and the exchanges between the BIBS modules are standard; the MFT intake of the OBPCS and PMS files is an extension to agree with BDOI IT.</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
           <t>Bank and channel files received automatically through the bank's managed file transfer, with control totals and a missing-file alert.</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>Agree the MFT folders and times with BDOI IT (Appendix S).</t>
+        </is>
+      </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Agree the MFT folders and times with BDOI IT (Appendix S).</t>
+          <t>FRS.CSH.05.01.04, 10.01, 10.02; Appendix N</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.05.01.04, 10.01, 10.02; Appendix N</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2588,40 +2543,35 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-131</t>
+          <t>INT-006 PMS post-dated cheque list (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>INT-006 PMS post-dated cheque list (OOTB: Partial)</t>
+          <t>File uploads with runs, records and alerts, and the exchanges between the BIBS modules are standard; the MFT intake of the OBPCS and PMS files is an extension to agree with BDOI IT.</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>File uploads with runs, records and alerts, and the exchanges between the BIBS modules are standard; the MFT intake of the OBPCS and PMS files is an extension to agree with BDOI IT.</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
           <t>Bank and channel files received automatically through the bank's managed file transfer, with control totals and a missing-file alert.</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>Agree the MFT folders and times with BDOI IT (Appendix S).</t>
+        </is>
+      </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>Agree the MFT folders and times with BDOI IT (Appendix S).</t>
+          <t>FRS.CSH.05.01.04, 10.01, 10.02; Appendix N</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.05.01.04, 10.01, 10.02; Appendix N</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2650,40 +2600,35 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-008</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Every upload and scheduled run processes each record on its own, logs the failed records and reports the run; failed runs are e-mailed.</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Every upload and scheduled run processes each record on its own, logs the failed records and reports the run; failed runs are e-mailed.</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
           <t>Partial processing with reprocessing of corrected rows and a run report; never a whole batch lost for one row.</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>Keep line-level processing also for the Commission Schedule (Appendix R, C10).</t>
+        </is>
+      </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>Keep line-level processing also for the Commission Schedule (Appendix R, C10).</t>
+          <t>FRS.CSH.05.01.12, 10.03</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.05.01.12, 10.03</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2712,40 +2657,35 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-004</t>
+          <t>BIL-020 Payment history at invoice level (Invoice 360) (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>BIL-020 Payment history at invoice level (Invoice 360) (OOTB: Partial)</t>
+          <t>Each booked account keeps its payment and remittance history with the AR numbers, view-only outside Cashiering.</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Each booked account keeps its payment and remittance history with the AR numbers, view-only outside Cashiering.</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
           <t>One view of an account with its payments, remittances and adjustments for every team.</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>FRS.CSH.08.01, 08.02</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.08.01, 08.02</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2774,40 +2714,35 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-011, FR-OP-013, FR-OP-014</t>
+          <t>BIL-003 Acknowledgement Receipt for premium (trust money) and non-premium payments (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>BIL-003 Acknowledgement Receipt for premium (trust money) and non-premium payments (OOTB: Partial)</t>
+          <t>Receipts with payor, references, amount, currency and mode, matched and applied at once, are standard; the posting step by a second user, the entry type and the bank account of BDOI's FRS are extensions (Appendix R, C1).</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Receipts with payor, references, amount, currency and mode, matched and applied at once, are standard; the posting step by a second user, the entry type and the bank account of BDOI's FRS are extensions (Appendix R, C1).</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
           <t>A receipt given to the payor at once, from a BIR-registered series; premium received by a broker held in trust for the insurer and identified to the insurer.</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Decide C1: issue at save with a daily review, or keep the posting step as a configurable approval.</t>
+        </is>
+      </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Decide C1: issue at save with a daily review, or keep the posting step as a configurable approval.</t>
+          <t>FRS.CSH.02.01, 02.05</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.01, 02.05</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2836,40 +2771,35 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-012, FR-OP-013</t>
+          <t>BIL-004 Official Receipt or sales invoice for broker income (OOTB: Available); TAX-013 EOPT-compliant sales invoices and supplementary documents (OOTB: Available)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>BIL-004 Official Receipt or sales invoice for broker income (OOTB: Available); TAX-013 EOPT-compliant sales invoices and supplementary documents (OOTB: Available)</t>
+          <t>Head Office receipts of income with VAT and withholding tax lines and the income account of each type are standard; the types are a maintained list.</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Head Office receipts of income with VAT and withholding tax lines and the income account of each type are standard; the types are a maintained list.</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
           <t>Under the Ease of Paying Taxes Act (RA 11976) the invoice is the primary document for services; series and forms registered with the BIR.</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Comptrollership (Tax) confirms the document name, form and series (Appendix R).</t>
+        </is>
+      </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>Comptrollership (Tax) confirms the document name, form and series (Appendix R).</t>
+          <t>FRS.CSH.02.02, 02.06; Appendix L</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.02, 02.06; Appendix L</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2898,40 +2828,35 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-013</t>
+          <t>BIL-005 Receipt cancellation and reinstatement with reason lists (OOTB: Partial); BIL-022 Returned (bounced) cheque handling (OOTB: Available)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>BIL-005 Receipt cancellation and reinstatement with reason lists (OOTB: Partial); BIL-022 Returned (bounced) cheque handling (OOTB: Available)</t>
+          <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
           <t>Every reversal of a receipt approved by a second person, with the reason, and the remitted premium recovered from the insurer.</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>Decide C2 (meaning of reinstatement) and C9 (remitted AR).</t>
+        </is>
+      </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>Decide C2 (meaning of reinstatement) and C9 (remitted AR).</t>
+          <t>FRS.CSH.03.01, 04.01</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.03.01, 04.01</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -2960,40 +2885,35 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-014</t>
+          <t>BIL-005 Receipt cancellation and reinstatement with reason lists (OOTB: Partial); BIL-022 Returned (bounced) cheque handling (OOTB: Available)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>BIL-005 Receipt cancellation and reinstatement with reason lists (OOTB: Partial); BIL-022 Returned (bounced) cheque handling (OOTB: Available)</t>
+          <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
           <t>Every reversal of a receipt approved by a second person, with the reason, and the remitted premium recovered from the insurer.</t>
         </is>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Decide C2 (meaning of reinstatement) and C9 (remitted AR).</t>
+        </is>
+      </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>Decide C2 (meaning of reinstatement) and C9 (remitted AR).</t>
+          <t>FRS.CSH.03.01, 04.01</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.03.01, 04.01</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3022,40 +2942,35 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-014</t>
+          <t>BIL-005 Receipt cancellation and reinstatement with reason lists (OOTB: Partial); BIL-022 Returned (bounced) cheque handling (OOTB: Available)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>BIL-005 Receipt cancellation and reinstatement with reason lists (OOTB: Partial); BIL-022 Returned (bounced) cheque handling (OOTB: Available)</t>
+          <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
           <t>Every reversal of a receipt approved by a second person, with the reason, and the remitted premium recovered from the insurer.</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Decide C2 (meaning of reinstatement) and C9 (remitted AR).</t>
+        </is>
+      </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>Decide C2 (meaning of reinstatement) and C9 (remitted AR).</t>
+          <t>FRS.CSH.03.01, 04.01</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.03.01, 04.01</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3084,40 +2999,35 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-010</t>
+          <t>BIL-006 Receipt numbering per branch with series depletion check (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>BIL-006 Receipt numbering per branch with series depletion check (OOTB: Partial)</t>
+          <t>Series per branch and kind with ATP, range, warning level and maker-checker; numbering under a lock and a depleted-series stop are standard.</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Series per branch and kind with ATP, range, warning level and maker-checker; numbering under a lock and a depleted-series stop are standard.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
           <t>Sequential numbers without gaps from the BIR-registered series; alert before depletion.</t>
         </is>
       </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>BDOI gives one format per receipt kind (Appendix R, C4).</t>
+        </is>
+      </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>BDOI gives one format per receipt kind (Appendix R, C4).</t>
+          <t>FRS.CSH.02.03, 02.05.08, 02.05.09</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.03, 02.05.08, 02.05.09</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3146,40 +3056,35 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-021</t>
+          <t>COM-003 Commission receipt per insurer payment or settlement (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>COM-003 Commission receipt per insurer payment or settlement (OOTB: Partial)</t>
+          <t>Commission payment details uploaded and issued as ORs per insurer and certificate are standard; the Commission Schedule matching and the trigger at the Disbursement approval of BDOI's FRS are extensions.</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Commission payment details uploaded and issued as ORs per insurer and certificate are standard; the Commission Schedule matching and the trigger at the Disbursement approval of BDOI's FRS are extensions.</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
           <t>One OR per insurer and settlement with the commission, VAT and withholding tax per account.</t>
         </is>
       </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Decide C11 and C12.</t>
+        </is>
+      </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Decide C11 and C12.</t>
+          <t>FRS.CSH.02.02, 02.05.14, 07.01</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.02, 02.05.14, 07.01</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3208,40 +3113,35 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-015, FR-OP-016</t>
+          <t>BIL-007 Upload of payment channel files (OOTB: Partial); BIL-008 Post-dated cheque warehouse (OOTB: Available); INT-006 PMS post-dated cheque list (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>BIL-007 Upload of payment channel files (OOTB: Partial); BIL-008 Post-dated cheque warehouse (OOTB: Available); INT-006 PMS post-dated cheque list (OOTB: Partial)</t>
+          <t>Uploads of the channel files with configurable layouts, duplicate refusal and the post-dated check warehouse with its daily maturity are standard; MFT intake, several files per event, file-name and header total checks are extensions.</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Uploads of the channel files with configurable layouts, duplicate refusal and the post-dated check warehouse with its daily maturity are standard; MFT intake, several files per event, file-name and header total checks are extensions.</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
           <t>Channel files received automatically with control totals; post-dated checks warehoused and turned into payments on maturity.</t>
         </is>
       </c>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>BDOI gives the layouts not yet given (Appendix S); decide C8 (Direct Credit) and C15 (PDC source).</t>
+        </is>
+      </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>BDOI gives the layouts not yet given (Appendix S); decide C8 (Direct Credit) and C15 (PDC source).</t>
+          <t>FRS.CSH.05.01, 05.02; Appendix D</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.05.01, 05.02; Appendix D</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3270,40 +3170,35 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-017</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
+          <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
         <is>
           <t>Removed from the BRD</t>
         </is>
       </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Section 2 (rows added with the reason)</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>Section 2 (rows added with the reason)</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3332,40 +3227,35 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-024</t>
+          <t>BIL-016 Receipt search and audit trail (OOTB: Available)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>BIL-016 Receipt search and audit trail (OOTB: Available)</t>
+          <t>Receipt search on the ten criteria, a search log and an audit trail that no user can change are standard.</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Receipt search on the ten criteria, a search log and an audit trail that no user can change are standard.</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
           <t>The seven items of the IT audit trail standard, refused actions included.</t>
         </is>
       </c>
-      <c r="I21" s="26" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the audit items and the search log retention (Appendix S).</t>
+        </is>
+      </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>Confirm the audit items and the search log retention (Appendix S).</t>
+          <t>FRS.CSH.08.01, 08.03</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.08.01, 08.03</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3394,40 +3284,35 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-024</t>
+          <t>BIL-016 Receipt search and audit trail (OOTB: Available)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>BIL-016 Receipt search and audit trail (OOTB: Available)</t>
+          <t>Receipt search on the ten criteria, a search log and an audit trail that no user can change are standard.</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Receipt search on the ten criteria, a search log and an audit trail that no user can change are standard.</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
           <t>The seven items of the IT audit trail standard, refused actions included.</t>
         </is>
       </c>
-      <c r="I22" s="26" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the audit items and the search log retention (Appendix S).</t>
+        </is>
+      </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>Confirm the audit items and the search log retention (Appendix S).</t>
+          <t>FRS.CSH.08.01, 08.03</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.08.01, 08.03</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3456,40 +3341,35 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-013, FR-OP-027</t>
+          <t>BIL-017 Automatic entries for receipt issuance, cancellation and reinstatement (OOTB: Available); ACC-002 Automatic journals from business events through posting rules (OOTB: Available)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>BIL-017 Automatic entries for receipt issuance, cancellation and reinstatement (OOTB: Available); ACC-002 Automatic journals from business events through posting rules (OOTB: Available)</t>
+          <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
           <t>Rules owned by the controller with maker-checker; foreign currency at the official rate with two decimals.</t>
         </is>
       </c>
-      <c r="I23" s="26" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>Comptrollership gives the accounts of Appendix I.</t>
+        </is>
+      </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>Comptrollership gives the accounts of Appendix I.</t>
+          <t>Appendix I</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>Appendix I</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3518,40 +3398,35 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-014, FR-OP-027</t>
+          <t>BIL-017 Automatic entries for receipt issuance, cancellation and reinstatement (OOTB: Available); ACC-002 Automatic journals from business events through posting rules (OOTB: Available)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>BIL-017 Automatic entries for receipt issuance, cancellation and reinstatement (OOTB: Available); ACC-002 Automatic journals from business events through posting rules (OOTB: Available)</t>
+          <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
           <t>Rules owned by the controller with maker-checker; foreign currency at the official rate with two decimals.</t>
         </is>
       </c>
-      <c r="I24" s="26" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>Comptrollership gives the accounts of Appendix I.</t>
+        </is>
+      </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>Comptrollership gives the accounts of Appendix I.</t>
+          <t>Appendix I</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>Appendix I</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3580,40 +3455,35 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-027</t>
+          <t>BIL-017 Automatic entries for receipt issuance, cancellation and reinstatement (OOTB: Available); ACC-002 Automatic journals from business events through posting rules (OOTB: Available)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>BIL-017 Automatic entries for receipt issuance, cancellation and reinstatement (OOTB: Available); ACC-002 Automatic journals from business events through posting rules (OOTB: Available)</t>
+          <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
           <t>Rules owned by the controller with maker-checker; foreign currency at the official rate with two decimals.</t>
         </is>
       </c>
-      <c r="I25" s="26" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Comptrollership gives the accounts of Appendix I.</t>
+        </is>
+      </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>Comptrollership gives the accounts of Appendix I.</t>
+          <t>Appendix I</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
-        <is>
-          <t>Appendix I</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3642,40 +3512,35 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-010</t>
+          <t>BIL-006 Receipt numbering per branch with series depletion check (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>BIL-006 Receipt numbering per branch with series depletion check (OOTB: Partial)</t>
+          <t>Series per branch and kind with ATP, range, warning level and maker-checker; numbering under a lock and a depleted-series stop are standard.</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Series per branch and kind with ATP, range, warning level and maker-checker; numbering under a lock and a depleted-series stop are standard.</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
           <t>Sequential numbers without gaps from the BIR-registered series; alert before depletion.</t>
         </is>
       </c>
-      <c r="I26" s="26" t="inlineStr">
+      <c r="H26" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>BDOI gives one format per receipt kind (Appendix R, C4).</t>
+        </is>
+      </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>BDOI gives one format per receipt kind (Appendix R, C4).</t>
+          <t>FRS.CSH.02.03, 02.05.08, 02.05.09</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.03, 02.05.08, 02.05.09</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3704,40 +3569,35 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-023</t>
+          <t>BIL-013 Automatic clearing of minimal balances (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>BIL-013 Automatic clearing of minimal balances (OOTB: Partial)</t>
+          <t>Minimal balances cleared when the payment is processed with a configurable threshold and the three exceptions are standard.</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Minimal balances cleared when the payment is processed with a configurable threshold and the three exceptions are standard.</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
           <t>Small differences cleared automatically under a threshold approved by the controller, never left in the unapplied list.</t>
         </is>
       </c>
-      <c r="I27" s="26" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Decide the threshold (Appendix R, C5).</t>
+        </is>
+      </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Decide the threshold (Appendix R, C5).</t>
+          <t>FRS.CSH.02.05.12</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.05.12</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3766,40 +3626,35 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-009</t>
+          <t>BIL-018 Cashiering reports with view-only and export permissions (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>BIL-018 Cashiering reports with view-only and export permissions (OOTB: Partial)</t>
+          <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
           <t>Daily cash reconciliation and ageing of unapplied payments for management.</t>
         </is>
       </c>
-      <c r="I28" s="26" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the filters and timing of Appendix M.</t>
+        </is>
+      </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the filters and timing of Appendix M.</t>
+          <t>FRS.CSH.09; Appendix M</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.09; Appendix M</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3828,40 +3683,35 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-009</t>
+          <t>BIL-018 Cashiering reports with view-only and export permissions (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>BIL-018 Cashiering reports with view-only and export permissions (OOTB: Partial)</t>
+          <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
           <t>Daily cash reconciliation and ageing of unapplied payments for management.</t>
         </is>
       </c>
-      <c r="I29" s="26" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the filters and timing of Appendix M.</t>
+        </is>
+      </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the filters and timing of Appendix M.</t>
+          <t>FRS.CSH.09; Appendix M</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.09; Appendix M</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3890,40 +3740,35 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-025</t>
+          <t>BIL-015 Batch printing of receipts (OOTB: Available)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>BIL-015 Batch printing of receipts (OOTB: Available)</t>
+          <t>Batch printing of receipts with a print log is standard; the ZIP of single PDFs, the certificate number and the REPRINT mark of BDOI's FRS are extensions.</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Batch printing of receipts with a print log is standard; the ZIP of single PDFs, the certificate number and the REPRINT mark of BDOI's FRS are extensions.</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
           <t>Re-printed receipts visibly marked; every print logged.</t>
         </is>
       </c>
-      <c r="I30" s="26" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the certificate number convention (Appendix R, C4).</t>
+        </is>
+      </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Confirm the certificate number convention (Appendix R, C4).</t>
+          <t>FRS.CSH.02.04</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.04</t>
-        </is>
-      </c>
-      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -3952,40 +3797,35 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-018, FR-OP-132</t>
+          <t>BIL-009 Automatic matching of payments to invoices (OOTB: Partial); BIL-011 Partial payments and instalment receipts (OOTB: Available)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>BIL-009 Automatic matching of payments to invoices (OOTB: Partial); BIL-011 Partial payments and instalment receipts (OOTB: Available)</t>
+          <t>Matching on the account references with pre-booked, excess, unmatched and cancelled-reference outcomes is standard; the legacy numbers as keys and the Direct Credit identification of BDOI's FRS are extensions.</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Matching on the account references with pre-booked, excess, unmatched and cancelled-reference outcomes is standard; the legacy numbers as keys and the Direct Credit identification of BDOI's FRS are extensions.</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
           <t>Straight-through matching of bank payments with the legacy references of migrated accounts.</t>
         </is>
       </c>
-      <c r="I31" s="26" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Load the legacy numbers with the migrated accounts (Appendix P).</t>
+        </is>
+      </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>Load the legacy numbers with the migrated accounts (Appendix P).</t>
+          <t>FRS.CSH.05.01.08, 05.03, 05.04</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.05.01.08, 05.03, 05.04</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4014,40 +3854,35 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-020</t>
+          <t>BIL-014 Non-premium receipts from insurers (AR Insurance) (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>BIL-014 Non-premium receipts from insurers (AR Insurance) (OOTB: Partial)</t>
+          <t>Non-premium receipts of insurers posted to AR Insurer the same day, apart from client premium.</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Non-premium receipts of insurers posted to AR Insurer the same day, apart from client premium.</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
           <t>Insurer refunds kept apart from client trust money.</t>
         </is>
       </c>
-      <c r="I32" s="26" t="inlineStr">
+      <c r="H32" s="26" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>FRS.CSH.02.01.15</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.01.15</t>
-        </is>
-      </c>
-      <c r="L32" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4076,40 +3911,35 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-019</t>
+          <t>BIL-010 Application by premium component hierarchy (OOTB: Not available); TAX-018 Premium taxes on billing and remittance (OOTB: Available)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>BIL-010 Application by premium component hierarchy (OOTB: Not available); TAX-018 Premium taxes on billing and remittance (OOTB: Available)</t>
+          <t>Application by component in a fixed order (DST, VAT, LGT, FST, other charges, basic premium), never to the premium due to the insurer.</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Application by component in a fixed order (DST, VAT, LGT, FST, other charges, basic premium), never to the premium due to the insurer.</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
           <t>Taxes collected first so that DST, VAT and LGT are always covered; order confirmed with the insurers.</t>
         </is>
       </c>
-      <c r="I33" s="26" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Decide C6 (FST and check before cash).</t>
+        </is>
+      </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>Decide C6 (FST and check before cash).</t>
+          <t>FRS.CSH.02.05.11</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.05.11</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4138,40 +3968,35 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-028</t>
+          <t>BIL-018 Cashiering reports with view-only and export permissions (OOTB: Partial)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>BIL-018 Cashiering reports with view-only and export permissions (OOTB: Partial)</t>
+          <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
           <t>Daily cash reconciliation and ageing of unapplied payments for management.</t>
         </is>
       </c>
-      <c r="I34" s="26" t="inlineStr">
+      <c r="H34" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>BDOI confirms the filters and timing of Appendix M.</t>
+        </is>
+      </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>BDOI confirms the filters and timing of Appendix M.</t>
+          <t>FRS.CSH.09; Appendix M</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.09; Appendix M</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4200,40 +4025,35 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-022</t>
+          <t>BIL-012 Unapplied and excess payment workbench with dispositions (OOTB: Not available)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>BIL-012 Unapplied and excess payment workbench with dispositions (OOTB: Not available)</t>
+          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
           <t>Every unapplied amount owned, aged and disposed with approval; refunds paid only by Disbursement.</t>
         </is>
       </c>
-      <c r="I35" s="26" t="inlineStr">
+      <c r="H35" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Decide C13 and C14 and the types needing approval (Appendix S).</t>
+        </is>
+      </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>Decide C13 and C14 and the types needing approval (Appendix S).</t>
+          <t>FRS.CSH.06</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.06</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4262,40 +4082,35 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-022</t>
+          <t>BIL-012 Unapplied and excess payment workbench with dispositions (OOTB: Not available)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>BIL-012 Unapplied and excess payment workbench with dispositions (OOTB: Not available)</t>
+          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
           <t>Every unapplied amount owned, aged and disposed with approval; refunds paid only by Disbursement.</t>
         </is>
       </c>
-      <c r="I36" s="26" t="inlineStr">
+      <c r="H36" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>Decide C13 and C14 and the types needing approval (Appendix S).</t>
+        </is>
+      </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Decide C13 and C14 and the types needing approval (Appendix S).</t>
+          <t>FRS.CSH.06</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.06</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4324,40 +4139,35 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
+          <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="26" t="inlineStr">
+      <c r="H37" s="26" t="inlineStr">
         <is>
           <t>Removed from the BRD</t>
         </is>
       </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Section 2 (rows added with the reason)</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>Section 2 (rows added with the reason)</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4386,40 +4196,35 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
+          <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="26" t="inlineStr">
+      <c r="H38" s="26" t="inlineStr">
         <is>
           <t>Removed from the BRD</t>
         </is>
       </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Section 2 (rows added with the reason)</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
-        <is>
-          <t>Section 2 (rows added with the reason)</t>
-        </is>
-      </c>
-      <c r="L38" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4448,40 +4253,35 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-120, FR-OP-121</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Specified in the FRS of Marketing Collection and Disbursement; Cashiering keeps the PR 2307 outstanding at payment.</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Specified with Marketing Collection and Disbursement in the BIBS FRS BRD-2; Cashiering keeps the PR 2307 outstanding at payment.</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
           <t>The certificate validated against the computed amount before the premium receivable is reversed.</t>
         </is>
       </c>
-      <c r="I39" s="26" t="inlineStr">
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>Specified in another FRS</t>
         </is>
       </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the owner FRS (Appendix R).</t>
+        </is>
+      </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>Confirm the owner FRS (Appendix R).</t>
+          <t>FRS.CSH.02.05.13</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.05.13</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4510,40 +4310,35 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-113</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Specified in the FRS of Marketing Collection and Disbursement; Cashiering keeps the PR 2307 outstanding at payment.</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Specified with Marketing Collection and Disbursement in the BIBS FRS BRD-2; Cashiering keeps the PR 2307 outstanding at payment.</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
           <t>The certificate validated against the computed amount before the premium receivable is reversed.</t>
         </is>
       </c>
-      <c r="I40" s="26" t="inlineStr">
+      <c r="H40" s="26" t="inlineStr">
         <is>
           <t>Specified in another FRS</t>
         </is>
       </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the owner FRS (Appendix R).</t>
+        </is>
+      </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>Confirm the owner FRS (Appendix R).</t>
+          <t>FRS.CSH.02.05.13</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.02.05.13</t>
-        </is>
-      </c>
-      <c r="L40" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4572,40 +4367,35 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-001, FR-OP-002</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Within the BIBS sizing for all BRDs</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Within the BIBS sizing for all BRDs</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-CAP-01)</t>
         </is>
       </c>
-      <c r="I41" s="26" t="inlineStr">
+      <c r="H41" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4634,40 +4424,35 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-002, FR-OP-008, FR-OP-015, FR-OP-016, FR-OP-018, FR-OP-019, FR-OP-025, FR-OP-131</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Assumed within the BIBS sizing; to confirm</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Assumed within the BIBS sizing; to confirm</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-CAP-02, NFR-CAP-03)</t>
         </is>
       </c>
-      <c r="I42" s="26" t="inlineStr">
+      <c r="H42" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4696,40 +4481,35 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-003</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Screens within 3 seconds for 95% of requests; file processing and printing run in the background with progress</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Screens within 3 seconds for 95% of requests; file processing and printing run in the background with progress</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-PRF-01, NFR-PRF-02, NFR-PRF-03)</t>
         </is>
       </c>
-      <c r="I43" s="26" t="inlineStr">
+      <c r="H43" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4758,40 +4538,35 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-024, FR-OP-025</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Print batches of up to 500 receipts</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Print batches of up to 500 receipts</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-PRF-06)</t>
         </is>
       </c>
-      <c r="I44" s="26" t="inlineStr">
+      <c r="H44" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4820,40 +4595,35 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-008, FR-OP-015</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Files up to 50 MB; each row processed on its own</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Files up to 50 MB; each row processed on its own</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-CAP-04, NFR-PRF-05)</t>
         </is>
       </c>
-      <c r="I45" s="26" t="inlineStr">
+      <c r="H45" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4882,40 +4652,35 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-008</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Runs scheduled outside the peak hours (Appendix M)</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Runs scheduled outside the peak hours (Appendix M)</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-CAP-05, NFR-PRF-07)</t>
         </is>
       </c>
-      <c r="I46" s="26" t="inlineStr">
+      <c r="H46" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -4949,35 +4714,30 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Same service window as BIBS</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Same service window as BIBS</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-AVL-01, NFR-AVL-02)</t>
         </is>
       </c>
-      <c r="I47" s="26" t="inlineStr">
+      <c r="H47" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5011,35 +4771,30 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Programme backup and recovery</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Programme backup and recovery</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-REC-01, NFR-REC-02, NFR-REC-03)</t>
         </is>
       </c>
-      <c r="I48" s="26" t="inlineStr">
+      <c r="H48" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5068,40 +4823,35 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-024</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Retention per record type</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Retention per record type</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-RET-01, NFR-RET-03)</t>
         </is>
       </c>
-      <c r="I49" s="26" t="inlineStr">
+      <c r="H49" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -5130,40 +4880,35 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Responsive screens; BDO-issued devices (FRS.OPS.001)</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Responsive screens; BDO-issued devices (FRS.OPS.001)</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-RSP-01, NFR-RSP-02)</t>
         </is>
       </c>
-      <c r="I50" s="26" t="inlineStr">
+      <c r="H50" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -5192,40 +4937,35 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-001, FR-OP-002</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Role-based access, segregation of duties, files stored read-only</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Role-based access, segregation of duties, files stored read-only</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-SEC-04, NFR-SEC-11)</t>
         </is>
       </c>
-      <c r="I51" s="26" t="inlineStr">
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -5254,40 +4994,35 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-024</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Audit trail that no user can change, refused actions recorded</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Audit trail that no user can change, refused actions recorded</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-AUD-01, NFR-AUD-02, NFR-AUD-03)</t>
         </is>
       </c>
-      <c r="I52" s="26" t="inlineStr">
+      <c r="H52" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -5316,40 +5051,35 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-003, FR-OP-022</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Amounts with thousands separators and two decimals; dates dd-MMM-yyyy; Philippine time</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Amounts with thousands separators and two decimals; dates dd-MMM-yyyy; Philippine time</t>
-        </is>
-      </c>
-      <c r="H53" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-LOC-02, NFR-LOC-03)</t>
         </is>
       </c>
-      <c r="I53" s="26" t="inlineStr">
+      <c r="H53" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
@@ -5378,51 +5108,46 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>FR-OP-023</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Parameters and lists of Appendix H changed without a change to the system</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Parameters and lists of Appendix H changed without a change to the system</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
           <t>BIBS standards for all BRDs (NFR register NFR-CFG-01, NFR-CFG-02)</t>
         </is>
       </c>
-      <c r="I54" s="26" t="inlineStr">
+      <c r="H54" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>Confirm the values of Appendix O (Appendix S).</t>
+          <t>Appendix O</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr">
-        <is>
           <t>Available</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L54"/>
+  <autoFilter ref="A4:K54"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I554">
+  <conditionalFormatting sqref="H5:H554">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Fit"</formula>
     </cfRule>
@@ -5430,13 +5155,13 @@
       <formula>"Configure"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:L554">
+  <conditionalFormatting sqref="A5:K554">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I554" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fit" error="Choose a value from the list (Fit)." type="list">
+    <dataValidation sqref="H5:H554" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fit" error="Choose a value from the list (Fit)." type="list">
       <formula1>'Lists'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$H$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$K$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$K$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Fit-Gap'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -863,7 +863,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Counts by fit: 36 BRD IDs and 14 non-functional rows</t>
+          <t>Counts by fit: 36 BRD IDs and 18 non-functional rows</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>FR items of the FRS v3.2</t>
+          <t>FR items of the FRS v3.3</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1434,7 +1434,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Counts by fit: 36 BRD IDs and 14 non-functional rows</t>
+          <t>Counts by fit: 36 BRD IDs and 18 non-functional rows</t>
         </is>
       </c>
     </row>
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>16</v>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>0</v>
@@ -2192,7 +2192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Peak: 15th and 30th of the month; 07:30-18:00</t>
+          <t>Peak: 15th and 30th of the month; peak hours 08:00-17:30</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -5142,12 +5142,240 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-15</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Maintenance: As per bank standard</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Non-functional (BRD Cashiering annex)</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Planned maintenance within the maintenance windows of the bank standard; users told in advance</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>BIBS standards for all BRDs (NFR register NFR-AVL-03)</t>
+        </is>
+      </c>
+      <c r="H55" s="26" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>Appendix O</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-16</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Disaster: Business continuity threshold: RTO 4 hours, RPO 24 hours</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Non-functional (BRD Cashiering annex)</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Programme disaster recovery; the targets of CSH-NFR-08 apply</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>BIBS standards for all BRDs (NFR register NFR-REC-01, NFR-REC-02)</t>
+        </is>
+      </c>
+      <c r="H56" s="26" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>Appendix O</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-17</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Sessions: Programme NFR 10.07 (Collections addendum): one session per device</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Non-functional (BRD Cashiering annex)</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.01.02</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>A second sign-in on another device ends the first (User Access Maintenance FRS)</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>BIBS standards for all BRDs (NFR register NFR 10.07)</t>
+        </is>
+      </c>
+      <c r="H57" s="26" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>Appendix O</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>CSH-NFR-18</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Audit source: Programme NFR 4.03 (CLM, CLXN, RI addenda): source / IP address in the audit log</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Non-functional (BRD Cashiering annex)</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.08.03</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>The audit log records the workstation / IP address of every action</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>BIBS standards for all BRDs (NFR register NFR 4.03)</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the values of Appendix O (Appendix S).</t>
+        </is>
+      </c>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>Appendix O</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K54"/>
+  <autoFilter ref="A4:K58"/>
   <mergeCells count="1">
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H554">
+  <conditionalFormatting sqref="H5:H558">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Fit"</formula>
     </cfRule>
@@ -5155,13 +5383,13 @@
       <formula>"Configure"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:K554">
+  <conditionalFormatting sqref="A5:K558">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H554" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fit" error="Choose a value from the list (Fit)." type="list">
+    <dataValidation sqref="H5:H558" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fit" error="Choose a value from the list (Fit)." type="list">
       <formula1>'Lists'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$H$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$K$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$J$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Fit-Gap'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -711,13 +711,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -746,6 +749,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -818,6 +822,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -885,6 +890,7 @@
         <v>54</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -964,6 +970,8 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="19" t="inlineStr">
         <is>
@@ -998,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1021,6 +1029,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1371,26 +1380,8 @@
       </c>
       <c r="D22" s="14" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Fit-Gap</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>In the BIBS environment</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Available / Partly available / Planned for</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D23"/>
+  <autoFilter ref="A4:D22"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2192,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2205,7 +2196,6 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2233,7 +2223,6 @@
       <c r="H3" s="24" t="n"/>
       <c r="I3" s="24" t="n"/>
       <c r="J3" s="24" t="n"/>
-      <c r="K3" s="24" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
@@ -2286,11 +2275,6 @@
           <t>Impact</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
-        <is>
-          <t>In the BIBS environment</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -2343,11 +2327,6 @@
           <t>FRS.CSH.01.01, 01.02; Appendix H</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -2400,11 +2379,6 @@
           <t>FRS.CSH.01.01, 01.02; Appendix H</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -2457,11 +2431,6 @@
           <t>FRS.CSH.01.03</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -2514,11 +2483,6 @@
           <t>FRS.CSH.05.01.04, 10.01, 10.02; Appendix N</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -2571,11 +2535,6 @@
           <t>FRS.CSH.05.01.04, 10.01, 10.02; Appendix N</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -2628,11 +2587,6 @@
           <t>FRS.CSH.05.01.12, 10.03</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -2685,11 +2639,6 @@
           <t>FRS.CSH.08.01, 08.02</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -2742,11 +2691,6 @@
           <t>FRS.CSH.02.01, 02.05</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -2799,11 +2743,6 @@
           <t>FRS.CSH.02.02, 02.06; Appendix L</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -2856,11 +2795,6 @@
           <t>FRS.CSH.03.01, 04.01</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -2913,11 +2847,6 @@
           <t>FRS.CSH.03.01, 04.01</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -2970,11 +2899,6 @@
           <t>FRS.CSH.03.01, 04.01</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -3027,11 +2951,6 @@
           <t>FRS.CSH.02.03, 02.05.08, 02.05.09</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -3084,11 +3003,6 @@
           <t>FRS.CSH.02.02, 02.05.14, 07.01</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -3141,11 +3055,6 @@
           <t>FRS.CSH.05.01, 05.02; Appendix D</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -3198,11 +3107,6 @@
           <t>Section 2 (rows added with the reason)</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -3255,11 +3159,6 @@
           <t>FRS.CSH.08.01, 08.03</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -3312,11 +3211,6 @@
           <t>FRS.CSH.08.01, 08.03</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -3369,11 +3263,6 @@
           <t>Appendix I</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -3426,11 +3315,6 @@
           <t>Appendix I</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -3483,11 +3367,6 @@
           <t>Appendix I</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -3540,11 +3419,6 @@
           <t>FRS.CSH.02.03, 02.05.08, 02.05.09</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -3597,11 +3471,6 @@
           <t>FRS.CSH.02.05.12</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3654,11 +3523,6 @@
           <t>FRS.CSH.09; Appendix M</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -3711,11 +3575,6 @@
           <t>FRS.CSH.09; Appendix M</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3768,11 +3627,6 @@
           <t>FRS.CSH.02.04</t>
         </is>
       </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -3825,11 +3679,6 @@
           <t>FRS.CSH.05.01.08, 05.03, 05.04</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3882,11 +3731,6 @@
           <t>FRS.CSH.02.01.15</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -3939,11 +3783,6 @@
           <t>FRS.CSH.02.05.11</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -3996,11 +3835,6 @@
           <t>FRS.CSH.09; Appendix M</t>
         </is>
       </c>
-      <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -4030,7 +3864,7 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
+          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of the platform.</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -4051,11 +3885,6 @@
       <c r="J35" s="12" t="inlineStr">
         <is>
           <t>FRS.CSH.06</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4087,7 +3916,7 @@
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
+          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of the platform.</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -4108,11 +3937,6 @@
       <c r="J36" s="12" t="inlineStr">
         <is>
           <t>FRS.CSH.06</t>
-        </is>
-      </c>
-      <c r="K36" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4167,11 +3991,6 @@
           <t>Section 2 (rows added with the reason)</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -4224,11 +4043,6 @@
           <t>Section 2 (rows added with the reason)</t>
         </is>
       </c>
-      <c r="K38" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -4281,11 +4095,6 @@
           <t>FRS.CSH.02.05.13</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -4338,11 +4147,6 @@
           <t>FRS.CSH.02.05.13</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -4372,7 +4176,7 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Within the BIBS sizing for all BRDs</t>
+          <t>Within the programme sizing for all BRDs</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -4393,11 +4197,6 @@
       <c r="J41" s="12" t="inlineStr">
         <is>
           <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4228,7 @@
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Assumed within the BIBS sizing; to confirm</t>
+          <t>Assumed within the programme sizing; to confirm</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -4450,11 +4249,6 @@
       <c r="J42" s="12" t="inlineStr">
         <is>
           <t>Appendix O</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4509,11 +4303,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -4566,11 +4355,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -4623,11 +4407,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -4680,11 +4459,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -4737,11 +4511,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -4794,11 +4563,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -4851,11 +4615,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -4908,11 +4667,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -4965,11 +4719,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -5022,11 +4771,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -5079,11 +4823,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -5136,11 +4875,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -5193,11 +4927,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -5250,11 +4979,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -5307,11 +5031,6 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -5364,16 +5083,11 @@
           <t>Appendix O</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K58"/>
+  <autoFilter ref="A4:J58"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H558">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
@@ -5383,7 +5097,7 @@
       <formula>"Configure"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:K558">
+  <conditionalFormatting sqref="A5:J558">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -989,7 +989,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1386,7 +1386,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2167,7 +2167,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5111,7 +5111,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5187,7 +5187,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_FitGap_BRD-02_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -5109,7 +5109,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
